--- a/nakasatsunai/dist/中札内村_確認結果入力シート_20261002.xlsx
+++ b/nakasatsunai/dist/中札内村_確認結果入力シート_20261002.xlsx
@@ -8,14 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認結果入力" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="凡例・記入要領" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認事項の詳細" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選択肢マスタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本文修正履歴" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="凡例・記入要領" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="確認事項の詳細" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="選択肢マスタ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'確認結果入力'!$A$4:$L$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'確認結果入力'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'確認事項の詳細'!$A$1:$G$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'本文修正履歴'!$A$5:$L$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'本文修正履歴'!$5:$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'確認事項の詳細'!$A$1:$G$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +99,28 @@
       <b val="1"/>
       <color rgb="002F6B45"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="000E5E62"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="00A33520"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <color rgb="002F6B45"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Yu Gothic"/>
+      <b val="1"/>
+      <color rgb="001F6F8B"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
@@ -202,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -264,10 +289,46 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -295,9 +356,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1885,6 +1943,1369 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>中札内村　経営戦略（案）　本文修正履歴</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>全24件（下水道20件・簡易水道4件／本文19件・図表5件）　／　適用日 2026-08-27 ・ 2026-10-01 ・ 2026-10-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>※　修正前／修正後の文言は、実際に適用したスクリプトから機械的に起こし、各版のファイル本体と突合（修正後の文言が存在し、修正前の文言が残っていないこと）を確認したもの。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>適用日</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>版</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>頁</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>箇所</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>修正前</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>修正後</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>根拠・指示元</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>関連ID</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>表紙</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>発行課名</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>建設課</t>
+        </is>
+      </c>
+      <c r="I6" s="25" t="inlineStr">
+        <is>
+          <t>施設課</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>発行課名／朱書き</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>p.2</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H7" s="29" t="inlineStr">
+        <is>
+          <t>町は札内川流域</t>
+        </is>
+      </c>
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>村は札内川流域</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>朱書き漏れ</t>
+        </is>
+      </c>
+      <c r="K7" s="16" t="inlineStr"/>
+      <c r="L7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>p.2</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>平成９（１９９７）年4月1日に供用を開始</t>
+        </is>
+      </c>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t>平成９（１９９７）年３月に供用を開始</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>公表版「平成8年度」と整合</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr"/>
+      <c r="L8" s="6" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>p.2</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H9" s="29" t="inlineStr">
+        <is>
+          <t>処理場は1箇所で、町の中心部</t>
+        </is>
+      </c>
+      <c r="I9" s="30" t="inlineStr">
+        <is>
+          <t>処理場は1箇所で、村の中心部</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>朱書き</t>
+        </is>
+      </c>
+      <c r="K9" s="16" t="inlineStr"/>
+      <c r="L9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>p.2</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>これまでの整備により、町全体</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t>これまでの整備により、村全体</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>朱書き</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr"/>
+      <c r="L10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>p.2</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr"/>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H11" s="29" t="inlineStr">
+        <is>
+          <t>令和５（２０２３）年４月からは地方公営企業法の全部適用へ移行し</t>
+        </is>
+      </c>
+      <c r="I11" s="30" t="inlineStr">
+        <is>
+          <t>令和４（２０２２）年４月からは地方公営企業法の一部適用（財務規定等の適用）へ移行し</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>朱書き＋論点A（公表版は一部適用）</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr"/>
+      <c r="L11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>p.20</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>本町における処理場</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t>本村における処理場</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>朱書き漏れ</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr"/>
+      <c r="L12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>p.20</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr"/>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H13" s="29" t="inlineStr">
+        <is>
+          <t>平成２２（２０１０）年度から供用開始し、令和６（２０２４）年度現在で１５年の稼働</t>
+        </is>
+      </c>
+      <c r="I13" s="30" t="inlineStr">
+        <is>
+          <t>平成８年度（平成９年３月）から供用開始し、令和６（２０２４）年度現在で２８年の稼働</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>公表版「供用開始年度＝平成8年度（28年）」</t>
+        </is>
+      </c>
+      <c r="K13" s="16" t="inlineStr"/>
+      <c r="L13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>p.26</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>国（県）補助金</t>
+        </is>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>国（道）補助金</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>朱書き</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr"/>
+      <c r="L14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>p.34</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr"/>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H15" s="29" t="inlineStr">
+        <is>
+          <t>●国（県）補助金</t>
+        </is>
+      </c>
+      <c r="I15" s="30" t="inlineStr">
+        <is>
+          <t>●国（道）補助金</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="inlineStr">
+        <is>
+          <t>朱書き</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="inlineStr"/>
+      <c r="L15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>p.34</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>国庫（県）補助対象事業</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>国庫（道）補助対象事業</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>朱書き</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr"/>
+      <c r="L16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>p.38</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr"/>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H17" s="29" t="inlineStr">
+        <is>
+          <t>町ホームページ</t>
+        </is>
+      </c>
+      <c r="I17" s="30" t="inlineStr">
+        <is>
+          <t>村ホームページ</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>朱書き</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="inlineStr"/>
+      <c r="L17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>20260827修正</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>p.10</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>組織図（SmartArt）</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>図表</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>町長</t>
+        </is>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>村長</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>朱書き</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>word/diagrams の data1.xml と drawing1.xml の2パートを更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>20261001修正</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>p.19</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr"/>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H19" s="29" t="inlineStr">
+        <is>
+          <t>令和５（20２３）年度末の時点で、下水道事業の総管渠延長は、１７１,３４７.05ｍ（管更生含む）に達し、村内での下水道普及率はほぼ１００％となっています。</t>
+        </is>
+      </c>
+      <c r="I19" s="30" t="inlineStr">
+        <is>
+          <t>令和５（２０２３）年度末の時点で、下水道事業の総管渠延長は、２５，２７０．６６ｍとなっています。村内での下水道普及率は６９．５％（令和５年度決算）であり、処理区域内の水洗化率は９８．５％と高い水準にあります。</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>提供資料「管渠延長.pdf」の合計値へ。普及率は経営比較分析表の値</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>A-2／B-4／B-5</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>基準時点は令和5年度末、普及率は経営比較分析表の値、管更生の但書は削除（いずれも要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>20261001修正</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>p.19</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>本計画期間中の１０年間で耐用年数を迎える管渠は全体の約２６％の昭和世代に布設された笹尾・城山地区のものです。今後の管渠の更新に向けて長期的な期間で管渠の長寿命化や更新に向けた対策が必要となっています。</t>
+        </is>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
+        <is>
+          <t>管渠は平成４（１９９２）年度以降に布設されており、最も古いもので令和７（２０２５）年度時点において３３年が経過しています。法定耐用年数（５０年）に達するのは令和２４（２０４２）年度以降となるため、本計画期間中に耐用年数を迎える管渠はありませんが、布設から３０年を超える管渠が全体の約４１％（１０，４７７ｍ）を占めることから、長期的な期間で管渠の長寿命化や更新に向けた対策が必要となっています。</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>他団体の地名・年代を削除し、提供資料の布設年度に基づく記述へ</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>B-5</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>法定耐用年数50年で再計算。計画期間中の到達はゼロ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>20261001修正</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>p.25</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr"/>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H21" s="29" t="inlineStr">
+        <is>
+          <t>管渠は古いもので約４０年が過ぎています。</t>
+        </is>
+      </c>
+      <c r="I21" s="30" t="inlineStr">
+        <is>
+          <t>管渠は古いもので３０年を超えています。</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>最古は平成4年度布設（令和7年度時点で33年）</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr"/>
+      <c r="L21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>20261001修正</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>p.25</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>計画期間中に全体の約１／４が耐用年数を迎えることから、更新に向けた資金の確保や長寿命化対策による対応が求められています。</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="inlineStr">
+        <is>
+          <t>計画期間中に耐用年数を迎える管渠はありませんが、布設から３０年を超える管渠が全体の約４割を占めることから、更新に向けた資金の確保や長寿命化対策による計画的な対応が求められています。</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>耐用年数到達の再計算結果を反映</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr"/>
+      <c r="L22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>20261001修正</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>《中札内村下水道処理区域図》</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>図表</t>
+        </is>
+      </c>
+      <c r="H23" s="29" t="inlineStr">
+        <is>
+          <t>（白紙）</t>
+        </is>
+      </c>
+      <c r="I23" s="30" t="inlineStr">
+        <is>
+          <t>提供資料「区域.pdf」を貼込（6.40×4.53in・中央揃え）</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>提供資料の反映</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr"/>
+      <c r="L23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>20261001修正</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>p.19</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>■公共下水道事業各年度整備延長</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>図表</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>他団体データ（1976〜2024年・総延長171,347.05m相当）</t>
+        </is>
+      </c>
+      <c r="I24" s="25" t="inlineStr">
+        <is>
+          <t>提供資料の年度別延長で再作成（平成4〜令和5年度・合計25,270.66m／6.53×4.26in）</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>提供資料の反映</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>A-2</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>20261001修正</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>p.20</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>■処理場の概要</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>図表</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="inlineStr">
+        <is>
+          <t>三戸浄化センターの諸元（3,180㎥/日・計画処理人口4,120人）</t>
+        </is>
+      </c>
+      <c r="I25" s="30" t="inlineStr">
+        <is>
+          <t>中札内浄化センターの諸元へ差替（1,520㎥/日＝760×2池・計画区域内人口2,661人／6.53×1.00in）</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>提供資料の反映</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr">
+        <is>
+          <t>主要施設の一覧は資料未入手のため表下に注記を付した</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>簡易水道</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>20261001修正</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>《中札内村給水区域図》</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>図表</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>（白紙）</t>
+        </is>
+      </c>
+      <c r="I26" s="25" t="inlineStr">
+        <is>
+          <t>受領Excel内の給水区域図を貼込（6.40×4.30in・中央揃え）</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>提供資料の反映</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr"/>
+      <c r="L26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>簡易水道</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>20261002修正</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Ⅱ-1（５）資産活用の状況 ❶エネルギー利用</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="inlineStr">
+        <is>
+          <t>（下水熱・下水汚泥・発電等）</t>
+        </is>
+      </c>
+      <c r="I27" s="30" t="inlineStr">
+        <is>
+          <t>（小水力発電等）</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>下水道側の朱書き指示と同一の誤り（ご承認済）</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>E-4</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>簡易水道の目次は「本文完成後調整」のため頁番号は未確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="21" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>簡易水道</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>20261002修正</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Ⅳ-3（２）❷収支計画のうち財源についての説明【資本的収入】</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>●国（県）補助金</t>
+        </is>
+      </c>
+      <c r="I28" s="25" t="inlineStr">
+        <is>
+          <t>●国（道）補助金</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>下水道側の朱書き指示と同一の誤り（ご承認済）</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>E-3</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>簡易水道の目次は「本文完成後調整」のため頁番号は未確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>簡易水道</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>20261002修正</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>Ⅳ-3（２）❷収支計画のうち財源についての説明【資本的収入】</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
+      <c r="H29" s="29" t="inlineStr">
+        <is>
+          <t>国庫（県）補助対象事業</t>
+        </is>
+      </c>
+      <c r="I29" s="30" t="inlineStr">
+        <is>
+          <t>国庫（道）補助対象事業</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>下水道側の朱書き指示と同一の誤り（ご承認済）</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>E-3</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>簡易水道の目次は「本文完成後調整」のため頁番号は未確定</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:L29"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B1:F25"/>
@@ -1899,21 +3320,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>記入要領</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t>１．ご記入いただく列</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>H　ご回答</t>
         </is>
@@ -1923,12 +3344,12 @@
           <t>一覧から選択（セルをクリックすると選択肢が出ます）。該当がなければ「その他」を選び、H列に内容をご記入ください。</t>
         </is>
       </c>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="24" t="n"/>
-      <c r="F4" s="25" t="n"/>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="37" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>I　補足・回答内容</t>
         </is>
@@ -1938,12 +3359,12 @@
           <t>自由記述。資料をご提供いただく事項（A-1・A-6）はファイル名や提供時期をご記入ください。</t>
         </is>
       </c>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="25" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="37" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>J　決定者</t>
         </is>
@@ -1953,12 +3374,12 @@
           <t>ご決定された方・部署名。</t>
         </is>
       </c>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="25" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="37" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>K　決定日</t>
         </is>
@@ -1968,27 +3389,27 @@
           <t>2026/10/15 の形式。</t>
         </is>
       </c>
-      <c r="D7" s="24" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="25" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="37" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>L　社内メモ</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>当方の作業メモ欄です。ご記入は不要です。</t>
         </is>
       </c>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="25" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="37" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>２．影響度の区分</t>
         </is>
@@ -2005,9 +3426,9 @@
           <t>収支計画・シミュレーション結果、または計画の根幹に関わる。未決のままでは本文を確定できない。</t>
         </is>
       </c>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="25" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="37" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="B12" s="15" t="inlineStr">
@@ -2020,9 +3441,9 @@
           <t>本文または図表の記載内容が変わる。影響は当該章で完結する。</t>
         </is>
       </c>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="24" t="n"/>
-      <c r="F12" s="25" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="37" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="B13" s="17" t="inlineStr">
@@ -2035,94 +3456,94 @@
           <t>表記・データ整理のレベル。他への波及はない。</t>
         </is>
       </c>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="25" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="37" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>３．記入例</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="28" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="40" t="inlineStr">
         <is>
           <t>ご回答</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="D16" s="40" t="inlineStr">
         <is>
           <t>補足・回答内容</t>
         </is>
       </c>
-      <c r="E16" s="28" t="inlineStr">
+      <c r="E16" s="40" t="inlineStr">
         <is>
           <t>決定者</t>
         </is>
       </c>
-      <c r="F16" s="28" t="inlineStr">
+      <c r="F16" s="40" t="inlineStr">
         <is>
           <t>決定日</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>B-4</t>
         </is>
       </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="C17" s="41" t="inlineStr">
         <is>
           <t>69.48%（経営比較分析表・普及率）</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="D17" s="41" t="inlineStr">
         <is>
           <t>公表している経営比較分析表の値に揃える。指標名も「普及率」とする。</t>
         </is>
       </c>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="41" t="inlineStr">
         <is>
           <t>施設課</t>
         </is>
       </c>
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="42" t="inlineStr">
         <is>
           <t>2026/10/15</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>※　上の行は記入例です。実際のご記入は「確認結果入力」シートにお願いします。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>４．回答状況</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>※　Excelで開くと自動計算されます。</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>確認事項の総数</t>
         </is>
@@ -2133,7 +3554,7 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>回答済み</t>
         </is>
@@ -2144,7 +3565,7 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="44" t="inlineStr">
         <is>
           <t>未回答</t>
         </is>
@@ -2155,7 +3576,7 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>うち影響度「大」の未回答</t>
         </is>
@@ -2180,7 +3601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3130,7 +4551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3148,46 +4569,46 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>※　このシートは「確認結果入力」シートのプルダウンの元データです。編集しないでください。</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>選択肢1</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="40" t="inlineStr">
         <is>
           <t>選択肢2</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="40" t="inlineStr">
         <is>
           <t>選択肢3</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="E2" s="40" t="inlineStr">
         <is>
           <t>選択肢4</t>
         </is>
       </c>
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="40" t="inlineStr">
         <is>
           <t>選択肢5</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>A-1</t>
         </is>
@@ -3214,7 +4635,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>A-2</t>
         </is>
@@ -3241,7 +4662,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>A-3</t>
         </is>
@@ -3273,7 +4694,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>A-4</t>
         </is>
@@ -3300,7 +4721,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>A-5</t>
         </is>
@@ -3327,7 +4748,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>A-6</t>
         </is>
@@ -3354,7 +4775,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>B-1</t>
         </is>
@@ -3386,7 +4807,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>B-2</t>
         </is>
@@ -3413,7 +4834,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>B-3</t>
         </is>
@@ -3440,7 +4861,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>B-4</t>
         </is>
@@ -3467,7 +4888,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>B-5</t>
         </is>
@@ -3494,7 +4915,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="33" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>C-1</t>
         </is>
@@ -3526,7 +4947,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>C-2</t>
         </is>
@@ -3558,7 +4979,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>C-3</t>
         </is>
@@ -3590,7 +5011,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>C-4</t>
         </is>
@@ -3617,7 +5038,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>D-1</t>
         </is>
@@ -3649,7 +5070,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>D-2</t>
         </is>
@@ -3681,7 +5102,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>D-3</t>
         </is>
@@ -3713,7 +5134,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>D-4</t>
         </is>
@@ -3740,7 +5161,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>E-1</t>
         </is>
@@ -3767,7 +5188,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>E-2</t>
         </is>
@@ -3799,7 +5220,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="33" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>E-3</t>
         </is>
@@ -3826,7 +5247,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>E-4</t>
         </is>
@@ -3858,7 +5279,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>E-5</t>
         </is>
